--- a/UTCUTS/A1_Outputs/reference_freeze/A-O_AR_Model_Base_Year.xlsx
+++ b/UTCUTS/A1_Outputs/reference_freeze/A-O_AR_Model_Base_Year.xlsx
@@ -6633,7 +6633,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD86FD1-0953-4930-BF5E-9DDD64B0F452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{610C5F63-B17A-4971-8DB3-B0DE552DADEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
